--- a/从零开始学Slots/从零开始学Slots-19-番外篇-用VB模拟1x3Slots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-19-番外篇-用VB模拟1x3Slots.xlsx
@@ -5564,6 +5564,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:K118" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6084,5 +6087,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N62" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-19-番外篇-用VB模拟1x3Slots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-19-番外篇-用VB模拟1x3Slots.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="143">
   <si>
     <r>
       <rPr>
@@ -4532,11 +4532,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -4720,7 +4721,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4847,6 +4848,18 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5696,8 +5709,8 @@
       <c r="B12" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="16" t="s">
-        <v>92</v>
+      <c r="C12" s="32">
+        <v>1</v>
       </c>
       <c r="D12" s="16"/>
     </row>
@@ -5806,8 +5819,8 @@
       <c r="D21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
-        <v>112</v>
+      <c r="A22" s="33">
+        <v>1</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>113</v>
@@ -5818,8 +5831,8 @@
       <c r="D22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>115</v>
+      <c r="A23" s="33">
+        <v>2</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>116</v>
@@ -5833,8 +5846,8 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>118</v>
+      <c r="A24" s="33">
+        <v>3</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>119</v>
@@ -5846,8 +5859,8 @@
       <c r="E24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
-        <v>121</v>
+      <c r="A25" s="33">
+        <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>122</v>
@@ -5859,8 +5872,8 @@
       <c r="E25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
-        <v>124</v>
+      <c r="A26" s="33">
+        <v>5</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>125</v>
@@ -5895,8 +5908,8 @@
       <c r="C29" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="23" t="s">
-        <v>131</v>
+      <c r="D29" s="34">
+        <v>0.95</v>
       </c>
       <c r="E29" s="23"/>
       <c r="F29" s="23"/>
@@ -6014,8 +6027,8 @@
         <f aca="false">IF(ABS(B15-0.96)&lt;0.0001,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="C38" s="22" t="s">
-        <v>137</v>
+      <c r="C38" s="33">
+        <v>12</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
